--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 1.699.734,09</t>
-  </si>
-  <si>
-    <t>R$ 9.138,36
-R$ 9.325,33</t>
+177</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 1.710.867,53</t>
+  </si>
+  <si>
+    <t>R$ 9.149,02
+R$ 9.335,55</t>
   </si>
   <si>
     <t>(5.7%)
 (4.0%)</t>
   </si>
   <si>
-    <t>96.7</t>
-  </si>
-  <si>
-    <t>(9.1%)</t>
-  </si>
-  <si>
-    <t>33.1%</t>
-  </si>
-  <si>
-    <t>(11.4%)</t>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>(9.2%)</t>
+  </si>
+  <si>
+    <t>33.2%</t>
+  </si>
+  <si>
+    <t>(11.3%)</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>27.8</t>
   </si>
   <si>
-    <t>63.0%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
+    <t>62.8%</t>
+  </si>
+  <si>
+    <t>11.5%</t>
   </si>
   <si>
     <t>6.0</t>
@@ -962,19 +962,19 @@
     <t>6.7</t>
   </si>
   <si>
-    <t>12.8</t>
+    <t>12.7</t>
   </si>
   <si>
     <t>19.4</t>
   </si>
   <si>
-    <t>68.3%</t>
-  </si>
-  <si>
-    <t>-R$ 49.088,98</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>68.4%</t>
+  </si>
+  <si>
+    <t>-R$ 49.422,18</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8722,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8758,27 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.047526815855617799</v>
+      </c>
+      <c r="R58" s="7">
+        <v>125</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.10071942446043169</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.40038817292768447</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.029430050370774886</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.012320989739020466</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00052679136008277759</v>
+      </c>
+      <c r="X58" s="8">
+        <v>25.836425773195877</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.46391752577319589</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.010309278350515464</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.5377952755905513</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.3771474226804123</v>
+      </c>
       <c r="AC58" s="8">
         <v>11.251636</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>16.395659375000001</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.83505154639175261</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-333.19999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15407,7 +15441,9 @@
       <c r="AB111" s="8">
         <v>2.8539235294117646</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.980391</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.913723529411765</v>
       </c>
@@ -15419,7 +15455,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15772,7 +15808,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16909,7 +16945,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17302,7 +17338,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18471,7 +18507,7 @@
         <v>-258.80000000000001</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20789,7 +20825,7 @@
         <v>-2724.3600000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22001,7 +22037,7 @@
         <v>-1004.66</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24079,7 +24115,9 @@
       <c r="AB179" s="8">
         <v>1.8164285714285715</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.9235699999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.88381</v>
       </c>
@@ -28164,7 +28202,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-177</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 1.710.867,53</t>
-  </si>
-  <si>
-    <t>R$ 9.149,02
-R$ 9.335,55</t>
-  </si>
-  <si>
-    <t>(5.7%)
-(4.0%)</t>
-  </si>
-  <si>
-    <t>96.9</t>
-  </si>
-  <si>
-    <t>(9.2%)</t>
-  </si>
-  <si>
-    <t>33.2%</t>
-  </si>
-  <si>
-    <t>(11.3%)</t>
+183</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>R$ 1.760.294,64</t>
+  </si>
+  <si>
+    <t>R$ 9.120,70
+R$ 9.299,56</t>
+  </si>
+  <si>
+    <t>(5.8%)
+(4.1%)</t>
+  </si>
+  <si>
+    <t>96.6</t>
+  </si>
+  <si>
+    <t>(9.1%)</t>
+  </si>
+  <si>
+    <t>32.3%</t>
+  </si>
+  <si>
+    <t>(11.8%)</t>
   </si>
   <si>
     <t>2.8%</t>
@@ -950,10 +950,10 @@
     <t>27.8</t>
   </si>
   <si>
-    <t>62.8%</t>
-  </si>
-  <si>
-    <t>11.5%</t>
+    <t>63.4%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
   </si>
   <si>
     <t>6.0</t>
@@ -968,13 +968,13 @@
     <t>19.4</t>
   </si>
   <si>
-    <t>68.4%</t>
-  </si>
-  <si>
-    <t>-R$ 49.422,18</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>68.5%</t>
+  </si>
+  <si>
+    <t>-R$ 50.270,16</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>15715.4</v>
+      </c>
+      <c r="P6" s="5">
+        <v>15715.4</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.12328036693129629</v>
+      </c>
+      <c r="R6" s="7">
+        <v>171</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.2127659574468086</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.30651476258956184</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.0016221095231429045</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.019247521539381755</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0046462387212543111</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.963164492753624</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.92753623188405798</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.007246376811594203</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>4.2420118343195261</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.1830920289855071</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.4621969999999997</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.417874637681159</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.96376811594202894</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11579.02</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11579.02</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.32588955481608872</v>
+      </c>
+      <c r="R24" s="7">
+        <v>133</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.22018348623853212</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.3470302322649067</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.018471122772048064</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.002095816398969861</v>
+      </c>
+      <c r="X24" s="8">
+        <v>28.763605102040813</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.9064596899224804</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.3943877551020414</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>20.406632653061223</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.61224489795918369</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-719.17999999999995</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5924,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6226.3299999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6226.3299999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.045100073183341083</v>
+      </c>
+      <c r="R36" s="7">
+        <v>66</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.081967213114754189</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.29735926300083676</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.0043278946024383541</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.048739225193653403</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.011270925248099604</v>
+      </c>
+      <c r="X36" s="8">
+        <v>26.106295555555558</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.8199459016393442</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.0488636363636363</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>11.19627</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>17.934073333333334</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.75555555555555554</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7845,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7881,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1237.9000000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1237.9000000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.34995168879179961</v>
+      </c>
+      <c r="R51" s="7">
+        <v>12</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.34766944018095158</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.016828499878827046</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.098140399062929151</v>
+      </c>
+      <c r="X51" s="8">
+        <v>52.122222222222227</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>8.7987153846153845</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>31.411111111111111</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>39.559258999999997</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>46.496299999999998</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12604,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>7832.1000000000004</v>
+      </c>
+      <c r="P89" s="5">
+        <v>7832.1000000000004</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.37772272625790648</v>
+      </c>
+      <c r="R89" s="7">
+        <v>75</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.3303571428571429</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.99094214833824901</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-1.3309109944970059</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.029020569196001073</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.012971233768721032</v>
+      </c>
+      <c r="X89" s="8">
+        <v>26.521905714285715</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.0921175675675681</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>3.8583323529411766</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>17.505714285714287</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16683,7 +16859,7 @@
         <v>-163.59999999999999</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18638,7 +18814,7 @@
         <v>-419.85000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20952,7 +21128,7 @@
         <v>44.5</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21346,7 +21522,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21382,25 +21558,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>6836.3599999999997</v>
+      </c>
+      <c r="P158" s="5">
+        <v>6836.3599999999997</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.41773365869031043</v>
+      </c>
+      <c r="R158" s="7">
+        <v>71</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.40336134453781514</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.30720713947188272</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.010827604163619237</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.027037853477581638</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0038573890198877769</v>
+      </c>
+      <c r="X158" s="8">
+        <v>33.670977586206895</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>8.8992957746478876</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>4.5672413793103441</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>13.708482999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>20.543677586206897</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.31034482758620691</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-128.80000000000001</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
